--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -26716,12 +26716,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -26755,16 +26755,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
-      </c>
-      <c r="P140" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="R140" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.5606928256970007</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -26773,12 +26770,12 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -26798,7 +26795,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -26811,42 +26808,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26878,12 +26875,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -26908,7 +26905,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -26917,47 +26914,44 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="O141" t="n">
-        <v>1</v>
-      </c>
-      <c r="P141" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis (Rotavirus)</t>
+          <t>Rotavirusinfektion</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
@@ -26967,7 +26961,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -26982,7 +26976,7 @@
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
@@ -27002,17 +26996,17 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined rotavirus category.</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -27035,7 +27029,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -27048,42 +27042,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27145,7 +27139,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -27307,7 +27301,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -27544,7 +27538,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -27553,16 +27547,16 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O144" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R144" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -27706,7 +27700,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -27715,13 +27709,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O145" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P145" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -27943,7 +27937,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -27952,16 +27946,16 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R146" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -28105,7 +28099,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -28114,13 +28108,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O147" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P147" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -28312,12 +28306,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -28342,22 +28336,25 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N148" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O148" t="n">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="P148" t="n">
+        <v>6</v>
       </c>
       <c r="R148" t="n">
-        <v>0.08080186002943539</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -28366,17 +28363,17 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
@@ -28386,12 +28383,12 @@
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -28399,47 +28396,47 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28471,12 +28468,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -28501,53 +28498,56 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O149" t="n">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="P149" t="n">
+        <v>6</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>case_notifications</t>
+          <t>sentinel_case_notifications</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
@@ -28557,7 +28557,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -28597,7 +28597,7 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Australia NINDSS rotavirus notifications.</t>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
@@ -28610,7 +28610,7 @@
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
@@ -28620,12 +28620,12 @@
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -28633,47 +28633,47 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28705,12 +28705,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -28744,13 +28744,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O150" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="R150" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.08080186002943539</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -28769,7 +28769,7 @@
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
@@ -28779,12 +28779,12 @@
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -28792,47 +28792,47 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28864,12 +28864,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -28903,24 +28903,24 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O151" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
@@ -28935,7 +28935,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -28950,7 +28950,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -28965,7 +28965,7 @@
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
@@ -28985,12 +28985,12 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1260.</t>
+          <t>Australia NINDSS rotavirus notifications.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -29003,7 +29003,7 @@
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
@@ -29013,12 +29013,12 @@
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AT151" t="n">
@@ -29026,47 +29026,47 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29098,12 +29098,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -29137,13 +29137,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -29172,12 +29172,12 @@
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -29185,47 +29185,47 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29257,12 +29257,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -29296,29 +29296,29 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Rotavirussykdom</t>
+          <t>Rotavirus</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -29343,7 +29343,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -29378,17 +29378,17 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1260.</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -29406,12 +29406,12 @@
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="AT153" t="n">
@@ -29419,45 +29419,438 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV153" t="inlineStr">
+      <c r="AV154" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW153" t="inlineStr">
+      <c r="AW154" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX153" t="inlineStr">
+      <c r="AX154" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY153" t="inlineStr">
+      <c r="AY154" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ153" t="inlineStr">
+      <c r="AZ154" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA153" t="inlineStr">
+      <c r="BA154" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB153" t="inlineStr">
+      <c r="BB154" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC153" t="inlineStr">
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Rotavirussykdom</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -29579,7 +29972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -29589,7 +29982,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -29609,7 +30002,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -29641,7 +30034,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8609</v>
+        <v>8669</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -20704,13 +20704,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="O106" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="R106" t="n">
-        <v>1.369958808680882</v>
+        <v>1.380977244139441</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -20863,10 +20863,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="O107" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -28705,12 +28705,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -28735,22 +28735,25 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O150" t="n">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="P150" t="n">
+        <v>4</v>
       </c>
       <c r="R150" t="n">
-        <v>0.08080186002943539</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -28759,17 +28762,17 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
@@ -28779,12 +28782,12 @@
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -28792,47 +28795,47 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28864,12 +28867,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -28894,53 +28897,56 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O151" t="n">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="P151" t="n">
+        <v>4</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>case_notifications</t>
+          <t>sentinel_case_notifications</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
@@ -28950,7 +28956,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -28990,7 +28996,7 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Australia NINDSS rotavirus notifications.</t>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -29003,7 +29009,7 @@
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
@@ -29013,12 +29019,12 @@
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_AU_ROTAVIRUS</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT151" t="n">
@@ -29026,47 +29032,47 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29098,12 +29104,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -29137,13 +29143,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O152" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="R152" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.08080186002943539</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -29152,7 +29158,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -29162,7 +29168,7 @@
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
@@ -29172,12 +29178,12 @@
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -29185,47 +29191,47 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29257,12 +29263,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -29296,24 +29302,24 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O153" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
@@ -29328,7 +29334,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -29343,7 +29349,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -29358,7 +29364,7 @@
       </c>
       <c r="AF153" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG153" t="inlineStr">
@@ -29378,12 +29384,12 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1260.</t>
+          <t>Australia NINDSS rotavirus notifications.</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -29396,7 +29402,7 @@
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
@@ -29406,12 +29412,12 @@
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_AU_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AT153" t="n">
@@ -29419,47 +29425,47 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29491,12 +29497,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -29530,13 +29536,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -29545,7 +29551,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -29565,12 +29571,12 @@
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="AT154" t="n">
@@ -29578,47 +29584,47 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29650,12 +29656,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -29689,29 +29695,29 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>Rotavirussykdom</t>
+          <t>Rotavirus</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -29736,7 +29742,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -29771,17 +29777,17 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1260.</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -29799,12 +29805,12 @@
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_110_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1260</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -29812,45 +29818,438 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV155" t="inlineStr">
+      <c r="AV156" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW155" t="inlineStr">
+      <c r="AW156" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX155" t="inlineStr">
+      <c r="AX156" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY155" t="inlineStr">
+      <c r="AY156" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ155" t="inlineStr">
+      <c r="AZ156" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA155" t="inlineStr">
+      <c r="BA156" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB155" t="inlineStr">
+      <c r="BB156" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC155" t="inlineStr">
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Rotavirussykdom</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -29972,7 +30371,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -29982,7 +30381,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -30002,7 +30401,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -30034,7 +30433,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8669</v>
+        <v>8676</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -26362,13 +26362,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O138" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R138" t="n">
-        <v>0.8844879128977531</v>
+        <v>0.9021776711557081</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -26521,10 +26521,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O139" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -29929,13 +29929,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -30088,10 +30088,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8676</v>
+        <v>8681</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -17077,7 +17077,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -24866,13 +24866,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="O129" t="n">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="R129" t="n">
-        <v>0.7088526811673195</v>
+        <v>1.443415045071277</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -25025,10 +25025,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="O130" t="n">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30433,7 +30433,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8681</v>
+        <v>8881</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -29536,13 +29536,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R154" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -29695,10 +29695,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -30252,6 +30252,405 @@
       <c r="BC157" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>3</v>
+      </c>
+      <c r="O158" t="n">
+        <v>3</v>
+      </c>
+      <c r="P158" t="n">
+        <v>3</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>3</v>
+      </c>
+      <c r="O159" t="n">
+        <v>3</v>
+      </c>
+      <c r="P159" t="n">
+        <v>3</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30288,7 +30687,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -30371,7 +30770,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -30381,7 +30780,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -30401,7 +30800,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -30433,7 +30832,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8881</v>
+        <v>8885</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -29929,13 +29929,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O156" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R156" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.2122770990954608</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -30088,10 +30088,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O157" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8885</v>
+        <v>8893</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -29536,13 +29536,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O154" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R154" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -29695,10 +29695,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8893</v>
+        <v>8896</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -24866,13 +24866,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O129" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="R129" t="n">
-        <v>1.443415045071277</v>
+        <v>1.447087856890797</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -25025,10 +25025,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O130" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8896</v>
+        <v>8897</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24714,7 +24714,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25107,7 +25107,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27395,7 +27395,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28592,7 +28592,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28991,7 +28991,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29384,7 +29384,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29536,13 +29536,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O154" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R154" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -29695,10 +29695,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O155" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -29929,13 +29929,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O156" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="R156" t="n">
-        <v>0.2122770990954608</v>
+        <v>0.3891746816750113</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -30088,10 +30088,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O157" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30649,6 +30649,405 @@
         </is>
       </c>
       <c r="BC159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>3</v>
+      </c>
+      <c r="O160" t="n">
+        <v>3</v>
+      </c>
+      <c r="P160" t="n">
+        <v>3</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>3</v>
+      </c>
+      <c r="O161" t="n">
+        <v>3</v>
+      </c>
+      <c r="P161" t="n">
+        <v>3</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -30687,7 +31086,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -30770,7 +31169,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -30780,7 +31179,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -30800,7 +31199,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -30832,7 +31231,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8897</v>
+        <v>8914</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -29143,13 +29143,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>22</v>
+        <v>384</v>
       </c>
       <c r="O152" t="n">
-        <v>22</v>
+        <v>384</v>
       </c>
       <c r="R152" t="n">
-        <v>0.08080186002943539</v>
+        <v>1.410359738695599</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -29302,10 +29302,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>22</v>
+        <v>384</v>
       </c>
       <c r="O153" t="n">
-        <v>22</v>
+        <v>384</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -29536,13 +29536,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O154" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R154" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -29695,10 +29695,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O155" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -31050,6 +31050,798 @@
       <c r="BC161" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>2</v>
+      </c>
+      <c r="O162" t="n">
+        <v>2</v>
+      </c>
+      <c r="P162" t="n">
+        <v>2</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="n">
+        <v>2</v>
+      </c>
+      <c r="P163" t="n">
+        <v>2</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Rotavirus</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1260.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -31086,7 +31878,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -31169,7 +31961,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -31179,7 +31971,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -31199,7 +31991,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -31231,7 +32023,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8914</v>
+        <v>9283</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -29143,13 +29143,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="O152" t="n">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="R152" t="n">
-        <v>1.410359738695599</v>
+        <v>1.450760668710317</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -29302,10 +29302,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="O153" t="n">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9283</v>
+        <v>9294</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -18573,7 +18573,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -22735,7 +22735,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -26613,7 +26613,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29929,13 +29929,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="O156" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R156" t="n">
-        <v>0.3891746816750113</v>
+        <v>0.548382505996607</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -30088,10 +30088,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="O157" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32023,7 +32023,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9294</v>
+        <v>9303</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -4082,6 +4082,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4227,6 +4232,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4363,6 +4373,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4499,6 +4514,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4635,6 +4655,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4771,6 +4796,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4907,6 +4937,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5043,6 +5078,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5179,6 +5219,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5315,6 +5360,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5451,6 +5501,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5587,6 +5642,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5723,6 +5783,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5859,6 +5924,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5995,6 +6065,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6131,6 +6206,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6267,6 +6347,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6403,6 +6488,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6539,6 +6629,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6675,6 +6770,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6811,6 +6911,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6947,6 +7052,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7083,6 +7193,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7219,6 +7334,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7355,6 +7475,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7491,6 +7616,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7627,6 +7757,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7763,6 +7898,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8530,7 +8670,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -13740,6 +13880,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13885,6 +14030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14021,6 +14171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14157,6 +14312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14293,6 +14453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14429,6 +14594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14565,6 +14735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14701,6 +14876,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14837,6 +15017,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14973,6 +15158,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15109,6 +15299,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15245,6 +15440,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15381,6 +15581,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15517,6 +15722,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15653,6 +15863,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15789,6 +16004,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15925,6 +16145,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16061,6 +16286,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16197,6 +16427,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16333,6 +16568,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16469,6 +16709,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16605,6 +16850,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16741,6 +16991,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16877,6 +17132,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17013,6 +17273,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17149,6 +17414,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17285,6 +17555,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17421,6 +17696,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18587,7 +18867,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -23641,6 +23921,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23786,6 +24071,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23922,6 +24212,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24058,6 +24353,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24194,6 +24494,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24330,6 +24635,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24466,6 +24776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24602,6 +24917,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24738,6 +25058,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24874,6 +25199,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25010,6 +25340,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25146,6 +25481,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25282,6 +25622,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25418,6 +25763,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25554,6 +25904,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25690,6 +26045,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25826,6 +26186,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25962,6 +26327,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26098,6 +26468,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26234,6 +26609,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26370,6 +26750,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26506,6 +26891,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26642,6 +27032,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26778,6 +27173,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26914,6 +27314,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27050,6 +27455,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27186,6 +27596,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27322,6 +27737,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28488,7 +28908,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33206,6 +33626,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33351,6 +33776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33487,6 +33917,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33623,6 +34058,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33759,6 +34199,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33895,6 +34340,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34031,6 +34481,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34167,6 +34622,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34303,6 +34763,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34439,6 +34904,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34575,6 +35045,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34711,6 +35186,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34847,6 +35327,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34983,6 +35468,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35119,6 +35609,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35255,6 +35750,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35391,6 +35891,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35527,6 +36032,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35663,6 +36173,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35799,6 +36314,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35935,6 +36455,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36071,6 +36596,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36207,6 +36737,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36343,6 +36878,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36479,6 +37019,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36615,6 +37160,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36751,6 +37301,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36887,6 +37442,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37654,7 +38214,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -43246,7 +43806,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -49228,7 +49788,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -55297,7 +55857,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -61366,7 +61926,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -63896,13 +64456,13 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="O360" t="n">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="R360" t="n">
-        <v>1.458106292349357</v>
+        <v>1.505852846003114</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -64055,10 +64615,10 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="O361" t="n">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="U361" t="inlineStr">
         <is>
@@ -67583,13 +68143,13 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O379" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R379" t="n">
-        <v>0.548382505996607</v>
+        <v>0.566072264254562</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
@@ -67742,10 +68302,10 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O380" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U380" t="inlineStr">
         <is>
@@ -67834,7 +68394,7 @@
       </c>
       <c r="AM380" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN380" t="b">
@@ -67937,12 +68497,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -67967,7 +68527,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -67976,16 +68536,13 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="O381" t="n">
-        <v>3</v>
-      </c>
-      <c r="P381" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="R381" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.3924849779879006</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -67994,12 +68551,12 @@
       </c>
       <c r="U381" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO381" t="inlineStr">
@@ -68019,7 +68576,7 @@
       </c>
       <c r="AS381" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AT381" t="n">
@@ -68032,42 +68589,42 @@
       </c>
       <c r="AV381" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA381" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB381" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC381" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -68099,12 +68656,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -68129,7 +68686,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -68138,47 +68695,44 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="O382" t="n">
-        <v>3</v>
-      </c>
-      <c r="P382" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="U382" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="V382" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="W382" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X382" t="inlineStr">
         <is>
-          <t>Infectious gastroenteritis (Rotavirus)</t>
+          <t>Rotavirusinfektion</t>
         </is>
       </c>
       <c r="Y382" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB382" t="inlineStr">
@@ -68188,7 +68742,7 @@
       </c>
       <c r="AC382" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD382" t="inlineStr">
@@ -68203,7 +68757,7 @@
       </c>
       <c r="AF382" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG382" t="inlineStr">
@@ -68223,17 +68777,17 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
         <is>
-          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined rotavirus category.</t>
         </is>
       </c>
       <c r="AM382" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN382" t="b">
@@ -68256,7 +68810,7 @@
       </c>
       <c r="AS382" t="inlineStr">
         <is>
-          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ROTAVIRUS</t>
         </is>
       </c>
       <c r="AT382" t="n">
@@ -68269,42 +68823,42 @@
       </c>
       <c r="AV382" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA382" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB382" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC382" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -68366,7 +68920,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -68528,7 +69082,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -68765,7 +69319,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -68774,16 +69328,16 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R385" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S385" t="inlineStr">
         <is>
@@ -68927,7 +69481,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -68936,13 +69490,13 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U386" t="inlineStr">
         <is>
@@ -69164,7 +69718,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -69173,16 +69727,16 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R387" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
@@ -69326,7 +69880,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -69335,13 +69889,13 @@
         </is>
       </c>
       <c r="N388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U388" t="inlineStr">
         <is>
@@ -69533,12 +70087,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -69563,22 +70117,25 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O389" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P389" t="n">
+        <v>1</v>
       </c>
       <c r="R389" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S389" t="inlineStr">
         <is>
@@ -69587,12 +70144,12 @@
       </c>
       <c r="U389" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO389" t="inlineStr">
@@ -69607,12 +70164,12 @@
       </c>
       <c r="AQ389" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS389" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT389" t="n">
@@ -69620,47 +70177,47 @@
       </c>
       <c r="AU389" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV389" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW389" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ389" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA389" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB389" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC389" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69692,12 +70249,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -69722,53 +70279,56 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N390" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O390" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P390" t="n">
+        <v>1</v>
       </c>
       <c r="U390" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="V390" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="W390" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X390" t="inlineStr">
         <is>
-          <t>Rotavirus</t>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
         </is>
       </c>
       <c r="Y390" t="inlineStr">
         <is>
-          <t>case_notifications</t>
+          <t>sentinel_case_notifications</t>
         </is>
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB390" t="inlineStr">
@@ -69778,7 +70338,7 @@
       </c>
       <c r="AC390" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD390" t="inlineStr">
@@ -69793,7 +70353,7 @@
       </c>
       <c r="AF390" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG390" t="inlineStr">
@@ -69813,12 +70373,12 @@
       </c>
       <c r="AJ390" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK390" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1260.</t>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
         </is>
       </c>
       <c r="AM390" t="inlineStr">
@@ -69841,12 +70401,12 @@
       </c>
       <c r="AQ390" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS390" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1260</t>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT390" t="n">
@@ -69854,47 +70414,833 @@
       </c>
       <c r="AU390" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV390" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW390" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX390" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY390" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA390" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB390" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC390" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>2</v>
+      </c>
+      <c r="O391" t="n">
+        <v>2</v>
+      </c>
+      <c r="R391" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO391" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP391" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ391" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS391" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="AT391" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU391" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV390" t="inlineStr">
+      <c r="AV391" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW390" t="inlineStr">
+      <c r="AW391" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX390" t="inlineStr">
+      <c r="AX391" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY390" t="inlineStr">
+      <c r="AY391" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ390" t="inlineStr">
+      <c r="AZ391" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA390" t="inlineStr">
+      <c r="BA391" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB390" t="inlineStr">
+      <c r="BB391" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC390" t="inlineStr">
+      <c r="BC391" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N392" t="n">
+        <v>2</v>
+      </c>
+      <c r="O392" t="n">
+        <v>2</v>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>Rotavirus</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD392" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE392" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF392" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG392" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH392" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI392" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ392" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK392" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1260.</t>
+        </is>
+      </c>
+      <c r="AM392" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN392" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO392" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP392" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ392" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS392" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1260</t>
+        </is>
+      </c>
+      <c r="AT392" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU392" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV392" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW392" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX392" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY392" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA392" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB392" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC392" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N393" t="n">
+        <v>2</v>
+      </c>
+      <c r="O393" t="n">
+        <v>2</v>
+      </c>
+      <c r="R393" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO393" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP393" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ393" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS393" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT393" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU393" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV393" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW393" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX393" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY393" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA393" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB393" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC393" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N394" t="n">
+        <v>2</v>
+      </c>
+      <c r="O394" t="n">
+        <v>2</v>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>Rotavirussykdom</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB394" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF394" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG394" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH394" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI394" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ394" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK394" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM394" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN394" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO394" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP394" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ394" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_110_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT394" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU394" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV394" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW394" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX394" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY394" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA394" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB394" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC394" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -70014,7 +71360,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -70024,7 +71370,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11">
@@ -70044,7 +71390,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -70076,7 +71422,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13287</v>
+        <v>13347</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -64456,13 +64456,13 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O360" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="R360" t="n">
-        <v>1.505852846003114</v>
+        <v>1.513198469642154</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -64615,10 +64615,10 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O361" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="U361" t="inlineStr">
         <is>
@@ -70918,13 +70918,13 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O393" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R393" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S393" t="inlineStr">
         <is>
@@ -71077,10 +71077,10 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O394" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U394" t="inlineStr">
         <is>
@@ -71241,6 +71241,405 @@
       <c r="BC394" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N395" t="n">
+        <v>1</v>
+      </c>
+      <c r="O395" t="n">
+        <v>1</v>
+      </c>
+      <c r="P395" t="n">
+        <v>1</v>
+      </c>
+      <c r="R395" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO395" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP395" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ395" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT395" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU395" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV395" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW395" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX395" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY395" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA395" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB395" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC395" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N396" t="n">
+        <v>1</v>
+      </c>
+      <c r="O396" t="n">
+        <v>1</v>
+      </c>
+      <c r="P396" t="n">
+        <v>1</v>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB396" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD396" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE396" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF396" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG396" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI396" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ396" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK396" t="inlineStr">
+        <is>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+        </is>
+      </c>
+      <c r="AM396" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN396" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO396" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP396" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ396" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS396" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU396" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV396" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW396" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX396" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY396" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA396" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB396" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC396" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -71277,7 +71676,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -71360,7 +71759,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -71370,7 +71769,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -71390,7 +71789,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -71422,7 +71821,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13347</v>
+        <v>13356</v>
       </c>
     </row>
     <row r="16">
